--- a/tools/importer/reports/import-product-listing.report.xlsx
+++ b/tools/importer/reports/import-product-listing.report.xlsx
@@ -52,7 +52,7 @@
     <t>eds-page</t>
   </si>
   <si>
-    <t>2026-10-28T04:28:34.686Z</t>
+    <t>2026-10-28T05:01:27.117Z</t>
   </si>
   <si>
     <t/>
@@ -70,7 +70,7 @@
     <t>index</t>
   </si>
   <si>
-    <t>2026-10-28T04:28:26.140Z</t>
+    <t>2026-10-28T05:01:15.417Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/index.plain.html</t>
@@ -85,7 +85,7 @@
     <t>nav</t>
   </si>
   <si>
-    <t>2026-10-28T04:28:30.505Z</t>
+    <t>2026-10-28T05:01:21.051Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/nav.plain.html</t>
@@ -103,7 +103,7 @@
     <t>product-listing</t>
   </si>
   <si>
-    <t>2026-10-28T04:30:19.469Z</t>
+    <t>2026-10-28T05:03:22.378Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/pages/index.plain.html</t>
@@ -121,7 +121,7 @@
     <t>recipe</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:02.553Z</t>
+    <t>2026-10-28T05:01:56.824Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/finger-fries-recipe.plain.html</t>
@@ -133,7 +133,7 @@
     <t>recipes/masala-noodle-soup</t>
   </si>
   <si>
-    <t>2026-10-28T04:28:43.097Z</t>
+    <t>2026-10-28T05:01:35.310Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/masala-noodle-soup.plain.html</t>
@@ -145,7 +145,7 @@
     <t>recipes/masala-omelette</t>
   </si>
   <si>
-    <t>2026-10-28T04:28:52.245Z</t>
+    <t>2026-10-28T05:01:46.774Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/masala-omelette.plain.html</t>
@@ -157,7 +157,7 @@
     <t>recipes/noodle-burger</t>
   </si>
   <si>
-    <t>2026-10-28T04:28:48.390Z</t>
+    <t>2026-10-28T05:01:41.348Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-burger.plain.html</t>
@@ -169,7 +169,7 @@
     <t>recipes/noodle-chaat</t>
   </si>
   <si>
-    <t>2026-10-28T04:28:57.534Z</t>
+    <t>2026-10-28T05:01:51.324Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-chaat.plain.html</t>
@@ -181,7 +181,7 @@
     <t>recipes/noodle-curry</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:07.000Z</t>
+    <t>2026-10-28T05:02:03.221Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-curry.plain.html</t>
@@ -193,7 +193,7 @@
     <t>recipes/noodle-cutlets</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:17.738Z</t>
+    <t>2026-10-28T05:02:13.519Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-cutlets.plain.html</t>
@@ -205,7 +205,7 @@
     <t>recipes/noodle-fried-rice</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:12.207Z</t>
+    <t>2026-10-28T05:02:07.406Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-fried-rice.plain.html</t>
@@ -217,7 +217,7 @@
     <t>recipes/noodle-manchurian</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:27.445Z</t>
+    <t>2026-10-28T05:02:25.712Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-manchurian.plain.html</t>
@@ -229,7 +229,7 @@
     <t>recipes/noodle-paratha</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:24.121Z</t>
+    <t>2026-10-28T05:02:19.496Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-paratha.plain.html</t>
@@ -241,7 +241,7 @@
     <t>recipes/noodle-pizza</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:32.045Z</t>
+    <t>2026-10-28T05:02:29.902Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-pizza.plain.html</t>
@@ -253,7 +253,7 @@
     <t>recipes/noodle-poha</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:36.545Z</t>
+    <t>2026-10-28T05:02:35.327Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-poha.plain.html</t>
@@ -265,7 +265,7 @@
     <t>recipes/noodle-pulao</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:39.937Z</t>
+    <t>2026-10-28T05:02:40.240Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-pulao.plain.html</t>
@@ -277,7 +277,7 @@
     <t>recipes/noodle-sandwich</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:45.186Z</t>
+    <t>2026-10-28T05:02:45.320Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-sandwich.plain.html</t>
@@ -289,7 +289,7 @@
     <t>recipes/noodle-spring-rolls</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:49.345Z</t>
+    <t>2026-10-28T05:02:51.278Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-spring-rolls.plain.html</t>
@@ -301,7 +301,7 @@
     <t>recipes/noodle-stir-fry</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:59.164Z</t>
+    <t>2026-10-28T05:03:02.126Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-stir-fry.plain.html</t>
@@ -313,7 +313,7 @@
     <t>recipes/noodle-tacos</t>
   </si>
   <si>
-    <t>2026-10-28T04:30:04.940Z</t>
+    <t>2026-10-28T05:03:07.758Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-tacos.plain.html</t>
@@ -325,7 +325,7 @@
     <t>recipes/noodle-upma</t>
   </si>
   <si>
-    <t>2026-10-28T04:30:10.802Z</t>
+    <t>2026-10-28T05:03:13.069Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-upma.plain.html</t>
@@ -337,7 +337,7 @@
     <t>recipes/noodles-chilla</t>
   </si>
   <si>
-    <t>2026-10-28T04:29:54.672Z</t>
+    <t>2026-10-28T05:02:57.241Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodles-chilla.plain.html</t>
